--- a/toolkit/idea-capture.xlsx
+++ b/toolkit/idea-capture.xlsx
@@ -557,9 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -605,7 +603,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Est. saving €/yr</t>
+          <t>Est. saving £/yr</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1483,7 +1481,7 @@
     <row r="70">
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Total est. saving €/yr →</t>
+          <t>Total est. saving £/yr →</t>
         </is>
       </c>
       <c r="E70" s="11">
